--- a/新機種製作需求一覽表2026 v2.xlsx
+++ b/新機種製作需求一覽表2026 v2.xlsx
@@ -764,13 +764,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>供應商確認</v>
+        <v>研發確認</v>
       </c>
       <c r="C40" t="str">
         <v>工程審核</v>
       </c>
       <c r="F40" t="str">
-        <v>研發確認</v>
+        <v>品保處審核</v>
       </c>
     </row>
   </sheetData>
